--- a/input/List of products_Plant_Location_Rates - line 2_New.xlsx
+++ b/input/List of products_Plant_Location_Rates - line 2_New.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myoffice.accenture.com/personal/anup_upasani_accenture_com/Documents/Documents/2026/Mondelez/SV/Solver input data validation/Scrubbed/scrubbed_data_V6/scrubbed_data_6/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anuja.das\intellij-workspace\mondelez-line-validation-ai\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{B68C0993-31C7-4374-8953-13E6E85E9EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A57CC218-44FF-428F-BB20-381588FACC01}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA693571-FADC-4E45-B703-251F49E03E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CDF061CF-179D-44FF-97A3-8BC0CFAE0FCD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CDF061CF-179D-44FF-97A3-8BC0CFAE0FCD}"/>
   </bookViews>
   <sheets>
-    <sheet name="Inf L2" sheetId="1" r:id="rId1"/>
+    <sheet name="LINE_B" sheetId="1" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
@@ -59,15 +59,15 @@
     <definedName name="_________e1" hidden="1">{"test","Core Scenario",FALSE,"Cash Flow Analysis"}</definedName>
     <definedName name="_________Jim1" hidden="1">{#N/A,#N/A,FALSE,"L&amp;M Performance";#N/A,#N/A,FALSE,"Brand Performance";#N/A,#N/A,FALSE,"Marlboro Performance"}</definedName>
     <definedName name="_________jim2" hidden="1">{#N/A,#N/A,FALSE,"L&amp;M Performance";#N/A,#N/A,FALSE,"Brand Performance";#N/A,#N/A,FALSE,"Marlboro Performance"}</definedName>
-    <definedName name="_________key11" hidden="1">'[2]OB Interest'!$C$140</definedName>
-    <definedName name="_________key3" hidden="1">'[2]OB Interest'!$D$140</definedName>
-    <definedName name="_________key5" hidden="1">'[2]OB Interest'!$C$140</definedName>
-    <definedName name="_________key55" hidden="1">'[2]OB Interest'!$C$140</definedName>
-    <definedName name="_________key66" hidden="1">'[2]OB Interest'!$D$140</definedName>
-    <definedName name="_________key8" hidden="1">'[2]OB Interest'!$D$140</definedName>
-    <definedName name="_________key9" hidden="1">'[2]OB Interest'!$C$140</definedName>
-    <definedName name="_________kry6" hidden="1">'[2]OB Interest'!$C$140</definedName>
-    <definedName name="_________ky2" hidden="1">'[2]OB Interest'!$C$140</definedName>
+    <definedName name="_________key11" hidden="1">'[1]OB Interest'!$C$140</definedName>
+    <definedName name="_________key3" hidden="1">'[1]OB Interest'!$D$140</definedName>
+    <definedName name="_________key5" hidden="1">'[1]OB Interest'!$C$140</definedName>
+    <definedName name="_________key55" hidden="1">'[1]OB Interest'!$C$140</definedName>
+    <definedName name="_________key66" hidden="1">'[1]OB Interest'!$D$140</definedName>
+    <definedName name="_________key8" hidden="1">'[1]OB Interest'!$D$140</definedName>
+    <definedName name="_________key9" hidden="1">'[1]OB Interest'!$C$140</definedName>
+    <definedName name="_________kry6" hidden="1">'[1]OB Interest'!$C$140</definedName>
+    <definedName name="_________ky2" hidden="1">'[1]OB Interest'!$C$140</definedName>
     <definedName name="_________NBV2" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="_________npd1" hidden="1">{#N/A,#N/A,FALSE,"L&amp;M Performance";#N/A,#N/A,FALSE,"Brand Performance";#N/A,#N/A,FALSE,"Marlboro Performance"}</definedName>
     <definedName name="_________po1" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
@@ -89,15 +89,15 @@
     <definedName name="________r" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="________VE2" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="_______jim2" hidden="1">{#N/A,#N/A,FALSE,"L&amp;M Performance";#N/A,#N/A,FALSE,"Brand Performance";#N/A,#N/A,FALSE,"Marlboro Performance"}</definedName>
-    <definedName name="_______key11" hidden="1">'[2]OB Interest'!$C$140</definedName>
-    <definedName name="_______key3" hidden="1">'[2]OB Interest'!$D$140</definedName>
-    <definedName name="_______key5" hidden="1">'[2]OB Interest'!$C$140</definedName>
-    <definedName name="_______key55" hidden="1">'[2]OB Interest'!$C$140</definedName>
-    <definedName name="_______key66" hidden="1">'[2]OB Interest'!$D$140</definedName>
-    <definedName name="_______key8" hidden="1">'[2]OB Interest'!$D$140</definedName>
-    <definedName name="_______key9" hidden="1">'[2]OB Interest'!$C$140</definedName>
-    <definedName name="_______kry6" hidden="1">'[2]OB Interest'!$C$140</definedName>
-    <definedName name="_______ky2" hidden="1">'[2]OB Interest'!$C$140</definedName>
+    <definedName name="_______key11" hidden="1">'[1]OB Interest'!$C$140</definedName>
+    <definedName name="_______key3" hidden="1">'[1]OB Interest'!$D$140</definedName>
+    <definedName name="_______key5" hidden="1">'[1]OB Interest'!$C$140</definedName>
+    <definedName name="_______key55" hidden="1">'[1]OB Interest'!$C$140</definedName>
+    <definedName name="_______key66" hidden="1">'[1]OB Interest'!$D$140</definedName>
+    <definedName name="_______key8" hidden="1">'[1]OB Interest'!$D$140</definedName>
+    <definedName name="_______key9" hidden="1">'[1]OB Interest'!$C$140</definedName>
+    <definedName name="_______kry6" hidden="1">'[1]OB Interest'!$C$140</definedName>
+    <definedName name="_______ky2" hidden="1">'[1]OB Interest'!$C$140</definedName>
     <definedName name="_______NBV2" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="_______npd1" hidden="1">{#N/A,#N/A,FALSE,"L&amp;M Performance";#N/A,#N/A,FALSE,"Brand Performance";#N/A,#N/A,FALSE,"Marlboro Performance"}</definedName>
     <definedName name="_______r" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
@@ -126,16 +126,16 @@
     <definedName name="_____e1" hidden="1">{"test","Core Scenario",FALSE,"Cash Flow Analysis"}</definedName>
     <definedName name="_____Jim1" hidden="1">{#N/A,#N/A,FALSE,"L&amp;M Performance";#N/A,#N/A,FALSE,"Brand Performance";#N/A,#N/A,FALSE,"Marlboro Performance"}</definedName>
     <definedName name="_____jim2" hidden="1">{#N/A,#N/A,FALSE,"L&amp;M Performance";#N/A,#N/A,FALSE,"Brand Performance";#N/A,#N/A,FALSE,"Marlboro Performance"}</definedName>
-    <definedName name="_____key11" hidden="1">'[2]OB Interest'!$C$140</definedName>
-    <definedName name="_____key3" hidden="1">'[2]OB Interest'!$D$140</definedName>
+    <definedName name="_____key11" hidden="1">'[1]OB Interest'!$C$140</definedName>
+    <definedName name="_____key3" hidden="1">'[1]OB Interest'!$D$140</definedName>
     <definedName name="_____key4" hidden="1">#REF!</definedName>
-    <definedName name="_____key5" hidden="1">'[2]OB Interest'!$C$140</definedName>
-    <definedName name="_____key55" hidden="1">'[2]OB Interest'!$C$140</definedName>
-    <definedName name="_____key66" hidden="1">'[2]OB Interest'!$D$140</definedName>
-    <definedName name="_____key8" hidden="1">'[2]OB Interest'!$D$140</definedName>
-    <definedName name="_____key9" hidden="1">'[2]OB Interest'!$C$140</definedName>
-    <definedName name="_____kry6" hidden="1">'[2]OB Interest'!$C$140</definedName>
-    <definedName name="_____ky2" hidden="1">'[2]OB Interest'!$C$140</definedName>
+    <definedName name="_____key5" hidden="1">'[1]OB Interest'!$C$140</definedName>
+    <definedName name="_____key55" hidden="1">'[1]OB Interest'!$C$140</definedName>
+    <definedName name="_____key66" hidden="1">'[1]OB Interest'!$D$140</definedName>
+    <definedName name="_____key8" hidden="1">'[1]OB Interest'!$D$140</definedName>
+    <definedName name="_____key9" hidden="1">'[1]OB Interest'!$C$140</definedName>
+    <definedName name="_____kry6" hidden="1">'[1]OB Interest'!$C$140</definedName>
+    <definedName name="_____ky2" hidden="1">'[1]OB Interest'!$C$140</definedName>
     <definedName name="_____NBV2" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="_____npd1" hidden="1">{#N/A,#N/A,FALSE,"L&amp;M Performance";#N/A,#N/A,FALSE,"Brand Performance";#N/A,#N/A,FALSE,"Marlboro Performance"}</definedName>
     <definedName name="_____po1" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
@@ -181,15 +181,15 @@
     <definedName name="___sr200000" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="___VE2" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="___xlfn.RTD" hidden="1">#NAME?</definedName>
-    <definedName name="__123Graph_A" hidden="1">'[3]WO CONV'!$GX$33:$GX$58</definedName>
-    <definedName name="__123Graph_B" hidden="1">'[3]WO CONV'!$GY$33:$GY$58</definedName>
-    <definedName name="__123Graph_C" hidden="1">'[3]WO CONV'!$GZ$33:$GZ$58</definedName>
-    <definedName name="__123Graph_D" hidden="1">'[3]WO CONV'!$HA$33:$HA$58</definedName>
-    <definedName name="__123Graph_E" hidden="1">'[3]WO CONV'!$HB$33:$HB$58</definedName>
-    <definedName name="__123Graph_F" hidden="1">'[3]WO CONV'!$HC$33:$HC$58</definedName>
-    <definedName name="__123Graph_LBL_A" hidden="1">'[4]sov tot'!#REF!</definedName>
-    <definedName name="__123Graph_LBL_B" hidden="1">'[4]sov tot'!#REF!</definedName>
-    <definedName name="__123Graph_X" hidden="1">'[5]otr.cred.'!#REF!</definedName>
+    <definedName name="__123Graph_A" hidden="1">'[2]WO CONV'!$GX$33:$GX$58</definedName>
+    <definedName name="__123Graph_B" hidden="1">'[2]WO CONV'!$GY$33:$GY$58</definedName>
+    <definedName name="__123Graph_C" hidden="1">'[2]WO CONV'!$GZ$33:$GZ$58</definedName>
+    <definedName name="__123Graph_D" hidden="1">'[2]WO CONV'!$HA$33:$HA$58</definedName>
+    <definedName name="__123Graph_E" hidden="1">'[2]WO CONV'!$HB$33:$HB$58</definedName>
+    <definedName name="__123Graph_F" hidden="1">'[2]WO CONV'!$HC$33:$HC$58</definedName>
+    <definedName name="__123Graph_LBL_A" hidden="1">'[3]sov tot'!#REF!</definedName>
+    <definedName name="__123Graph_LBL_B" hidden="1">'[3]sov tot'!#REF!</definedName>
+    <definedName name="__123Graph_X" hidden="1">'[4]otr.cred.'!#REF!</definedName>
     <definedName name="__a10" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="__a11" hidden="1">{"rf19",#N/A,FALSE,"RF19";"rf20",#N/A,FALSE,"RF20";"rf20a",#N/A,FALSE,"RF20A";"rf21",#N/A,FALSE,"RF21";"rf21a",#N/A,FALSE,"RF21A";"rf21b",#N/A,FALSE,"RF21B";"rf22",#N/A,FALSE,"RF22";"rf22a",#N/A,FALSE,"RF22A";"rf22b",#N/A,FALSE,"RF22B"}</definedName>
     <definedName name="__a12" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
@@ -265,7 +265,7 @@
     <definedName name="_f" hidden="1">#REF!</definedName>
     <definedName name="_fc" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="_Fill" hidden="1">#REF!</definedName>
-    <definedName name="_FilterDatabase2" hidden="1">[6]DATOS!$A$4:$FM$326</definedName>
+    <definedName name="_FilterDatabase2" hidden="1">[5]DATOS!$A$4:$FM$326</definedName>
     <definedName name="_Jim1" hidden="1">{#N/A,#N/A,FALSE,"L&amp;M Performance";#N/A,#N/A,FALSE,"Brand Performance";#N/A,#N/A,FALSE,"Marlboro Performance"}</definedName>
     <definedName name="_jim2" hidden="1">{#N/A,#N/A,FALSE,"L&amp;M Performance";#N/A,#N/A,FALSE,"Brand Performance";#N/A,#N/A,FALSE,"Marlboro Performance"}</definedName>
     <definedName name="_Key1" hidden="1">#REF!</definedName>
@@ -327,11 +327,11 @@
     <definedName name="amor" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="an" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="ANGE" hidden="1">{#N/A,#N/A,FALSE,"L&amp;M Performance";#N/A,#N/A,FALSE,"Brand Performance";#N/A,#N/A,FALSE,"Marlboro Performance"}</definedName>
-    <definedName name="año2008">'[7]AÑO 2008'!$B$6:$AM$135</definedName>
+    <definedName name="año2008">'[6]AÑO 2008'!$B$6:$AM$135</definedName>
     <definedName name="año2009">#REF!</definedName>
     <definedName name="anscount" hidden="1">1</definedName>
-    <definedName name="aqwder" hidden="1">'[4]sov tot'!#REF!</definedName>
-    <definedName name="aqwz" hidden="1">'[4]sov tot'!#REF!</definedName>
+    <definedName name="aqwder" hidden="1">'[3]sov tot'!#REF!</definedName>
+    <definedName name="aqwz" hidden="1">'[3]sov tot'!#REF!</definedName>
     <definedName name="as">#REF!</definedName>
     <definedName name="asa" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="ASD" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
@@ -349,8 +349,8 @@
     <definedName name="Assumption" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="aum" hidden="1">{"test","Core Scenario",FALSE,"Cash Flow Analysis"}</definedName>
     <definedName name="ax" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
-    <definedName name="azeaq" hidden="1">'[4]sov tot'!#REF!</definedName>
-    <definedName name="AZERT" hidden="1">'[4]sov tot'!#REF!</definedName>
+    <definedName name="azeaq" hidden="1">'[3]sov tot'!#REF!</definedName>
+    <definedName name="AZERT" hidden="1">'[3]sov tot'!#REF!</definedName>
     <definedName name="B" hidden="1">#REF!</definedName>
     <definedName name="Bag" hidden="1">{"test","Core Scenario",FALSE,"Cash Flow Analysis"}</definedName>
     <definedName name="BALANCE_1999">#REF!</definedName>
@@ -377,9 +377,9 @@
     <definedName name="bv" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="cap" hidden="1">{"test","Core Scenario",FALSE,"Cash Flow Analysis"}</definedName>
     <definedName name="Capacity" hidden="1">{"test","Core Scenario",FALSE,"Cash Flow Analysis"}</definedName>
-    <definedName name="CAPEX98" hidden="1">[8]FINALPHP!$G$27</definedName>
+    <definedName name="CAPEX98" hidden="1">[7]FINALPHP!$G$27</definedName>
     <definedName name="CapexbyType_Ges" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
-    <definedName name="CapexComplVictoriData" hidden="1">'[9]otr.cred.'!#REF!</definedName>
+    <definedName name="CapexComplVictoriData" hidden="1">'[8]otr.cred.'!#REF!</definedName>
     <definedName name="carlkios" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="carlos" hidden="1">{"rf19",#N/A,FALSE,"RF19";"rf20",#N/A,FALSE,"RF20";"rf20a",#N/A,FALSE,"RF20A";"rf21",#N/A,FALSE,"RF21";"rf21a",#N/A,FALSE,"RF21A";"rf21b",#N/A,FALSE,"RF21B";"rf22",#N/A,FALSE,"RF22";"rf22a",#N/A,FALSE,"RF22A";"rf22b",#N/A,FALSE,"RF22B"}</definedName>
     <definedName name="carlos_1" hidden="1">{"test","Core Scenario",FALSE,"Cash Flow Analysis"}</definedName>
@@ -410,19 +410,19 @@
     <definedName name="control4">#REF!</definedName>
     <definedName name="Control5">#REF!</definedName>
     <definedName name="cpsp" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
-    <definedName name="CU">[10]galleteria!#REF!</definedName>
+    <definedName name="CU">[9]galleteria!#REF!</definedName>
     <definedName name="Currency">#REF!</definedName>
     <definedName name="d" hidden="1">#REF!</definedName>
     <definedName name="DADASDFSD" hidden="1">{#N/A,#N/A,FALSE,"L&amp;M Performance";#N/A,#N/A,FALSE,"Brand Performance";#N/A,#N/A,FALSE,"Marlboro Performance"}</definedName>
     <definedName name="data1" hidden="1">#REF!</definedName>
     <definedName name="data2" hidden="1">#REF!</definedName>
     <definedName name="data3" hidden="1">#REF!</definedName>
-    <definedName name="data4" hidden="1">'[11]#ref'!#REF!</definedName>
+    <definedName name="data4" hidden="1">'[10]#ref'!#REF!</definedName>
     <definedName name="dataGE16">#REF!</definedName>
     <definedName name="DATAVTA">#REF!</definedName>
-    <definedName name="date">[11]DATE!$B$5:$F$503</definedName>
+    <definedName name="date">[10]DATE!$B$5:$F$503</definedName>
     <definedName name="Date_BS">#REF!</definedName>
-    <definedName name="date2">[11]DATE!$C$5:$F$503</definedName>
+    <definedName name="date2">[10]DATE!$C$5:$F$503</definedName>
     <definedName name="DATOS">#REF!</definedName>
     <definedName name="dd" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="dddd" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
@@ -443,7 +443,7 @@
     <definedName name="dfgdgdfg" hidden="1">#REF!</definedName>
     <definedName name="dfs" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="dfsdasdf" hidden="1">{"rf19",#N/A,FALSE,"RF19";"rf20",#N/A,FALSE,"RF20";"rf20a",#N/A,FALSE,"RF20A";"rf21",#N/A,FALSE,"RF21";"rf21a",#N/A,FALSE,"RF21A";"rf21b",#N/A,FALSE,"RF21B";"rf22",#N/A,FALSE,"RF22";"rf22a",#N/A,FALSE,"RF22A";"rf22b",#N/A,FALSE,"RF22B"}</definedName>
-    <definedName name="dic">[7]DEC!$C$6:$DM$146</definedName>
+    <definedName name="dic">[6]DEC!$C$6:$DM$146</definedName>
     <definedName name="Discount" hidden="1">#REF!</definedName>
     <definedName name="display_area_2" hidden="1">#REF!</definedName>
     <definedName name="DIST_CHOCOLATES">#REF!</definedName>
@@ -505,7 +505,7 @@
     <definedName name="findme9" hidden="1">{#N/A,#N/A,FALSE,"Assumptions";#N/A,#N/A,FALSE,"1997 P&amp;L(pk) Estrada";#N/A,#N/A,FALSE,"ONGOING P&amp;L(pk) Estrada"}</definedName>
     <definedName name="Fix_Assets">#REF!</definedName>
     <definedName name="fj" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
-    <definedName name="FORM">[12]MasterData!$E$2:$E$56</definedName>
+    <definedName name="FORM">[11]MasterData!$E$2:$E$56</definedName>
     <definedName name="FSD" hidden="1">{"test","Core Scenario",FALSE,"Cash Flow Analysis"}</definedName>
     <definedName name="fsqsqfd" hidden="1">{"rf19",#N/A,FALSE,"RF19";"rf20",#N/A,FALSE,"RF20";"rf20a",#N/A,FALSE,"RF20A";"rf21",#N/A,FALSE,"RF21";"rf21a",#N/A,FALSE,"RF21A";"rf21b",#N/A,FALSE,"RF21B";"rf22",#N/A,FALSE,"RF22";"rf22a",#N/A,FALSE,"RF22A";"rf22b",#N/A,FALSE,"RF22B"}</definedName>
     <definedName name="GABY" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
@@ -524,13 +524,13 @@
     <definedName name="gg" hidden="1">{"test","Core Scenario",FALSE,"Cash Flow Analysis"}</definedName>
     <definedName name="ggggggggg" hidden="1">{#N/A,#N/A,FALSE,"L&amp;M Performance";#N/A,#N/A,FALSE,"Brand Performance";#N/A,#N/A,FALSE,"Marlboro Performance"}</definedName>
     <definedName name="GHJ" hidden="1">{"test","Core Scenario",FALSE,"Cash Flow Analysis"}</definedName>
-    <definedName name="goal_2008">'[7]Goals 2008'!$B$5:$P$18</definedName>
+    <definedName name="goal_2008">'[6]Goals 2008'!$B$5:$P$18</definedName>
     <definedName name="Graficos" hidden="1">{#N/A,#N/A,FALSE,"L&amp;M Performance";#N/A,#N/A,FALSE,"Brand Performance";#N/A,#N/A,FALSE,"Marlboro Performance"}</definedName>
     <definedName name="Grageas" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
-    <definedName name="graph">[13]Sheet2!$G$5:$G$13</definedName>
+    <definedName name="graph">[12]Sheet2!$G$5:$G$13</definedName>
     <definedName name="gsdfaga" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="gsdfga" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
-    <definedName name="gsegtregtaert" hidden="1">'[9]otr.cred.'!#REF!</definedName>
+    <definedName name="gsegtregtaert" hidden="1">'[8]otr.cred.'!#REF!</definedName>
     <definedName name="gsfgfs" hidden="1">{"rf19",#N/A,FALSE,"RF19";"rf20",#N/A,FALSE,"RF20";"rf20a",#N/A,FALSE,"RF20A";"rf21",#N/A,FALSE,"RF21";"rf21a",#N/A,FALSE,"RF21A";"rf21b",#N/A,FALSE,"RF21B";"rf22",#N/A,FALSE,"RF22";"rf22a",#N/A,FALSE,"RF22A";"rf22b",#N/A,FALSE,"RF22B"}</definedName>
     <definedName name="GUSTAVO" hidden="1">{#N/A,#N/A,FALSE,"DIA21 (2)";#N/A,#N/A,FALSE,"DIA21 (2)"}</definedName>
     <definedName name="gustavo_prueba" hidden="1">{#N/A,#N/A,FALSE,"DIA21 (2)";#N/A,#N/A,FALSE,"DIA21 (2)"}</definedName>
@@ -546,18 +546,18 @@
     <definedName name="ILT" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="inde" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="Index" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
-    <definedName name="INDICADORES_ABR00">'[14]menu principal'!#REF!</definedName>
-    <definedName name="INDICADORES_AGO00">'[14]menu principal'!#REF!</definedName>
-    <definedName name="INDICADORES_ENE00">'[14]menu principal'!#REF!</definedName>
-    <definedName name="INDICADORES_FEB00">'[14]menu principal'!#REF!</definedName>
-    <definedName name="INDICADORES_IIIQ">'[14]menu principal'!#REF!</definedName>
-    <definedName name="INDICADORES_IIQ">'[14]menu principal'!#REF!</definedName>
-    <definedName name="INDICADORES_IQ">'[14]menu principal'!#REF!</definedName>
-    <definedName name="INDICADORES_JUL00">'[14]menu principal'!#REF!</definedName>
-    <definedName name="INDICADORES_JUN00">'[14]menu principal'!#REF!</definedName>
-    <definedName name="INDICADORES_MAR00">'[14]menu principal'!#REF!</definedName>
-    <definedName name="INDICADORES_MAY00">'[14]menu principal'!#REF!</definedName>
-    <definedName name="INDICADORES_SET00">'[14]menu principal'!#REF!</definedName>
+    <definedName name="INDICADORES_ABR00">'[13]menu principal'!#REF!</definedName>
+    <definedName name="INDICADORES_AGO00">'[13]menu principal'!#REF!</definedName>
+    <definedName name="INDICADORES_ENE00">'[13]menu principal'!#REF!</definedName>
+    <definedName name="INDICADORES_FEB00">'[13]menu principal'!#REF!</definedName>
+    <definedName name="INDICADORES_IIIQ">'[13]menu principal'!#REF!</definedName>
+    <definedName name="INDICADORES_IIQ">'[13]menu principal'!#REF!</definedName>
+    <definedName name="INDICADORES_IQ">'[13]menu principal'!#REF!</definedName>
+    <definedName name="INDICADORES_JUL00">'[13]menu principal'!#REF!</definedName>
+    <definedName name="INDICADORES_JUN00">'[13]menu principal'!#REF!</definedName>
+    <definedName name="INDICADORES_MAR00">'[13]menu principal'!#REF!</definedName>
+    <definedName name="INDICADORES_MAY00">'[13]menu principal'!#REF!</definedName>
+    <definedName name="INDICADORES_SET00">'[13]menu principal'!#REF!</definedName>
     <definedName name="ISAURA" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="Itens_Desp">#REF!</definedName>
     <definedName name="iu" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
@@ -574,21 +574,21 @@
     <definedName name="jun">#REF!</definedName>
     <definedName name="k" hidden="1">#REF!</definedName>
     <definedName name="kdfj" hidden="1">{"rf19",#N/A,FALSE,"RF19";"rf20",#N/A,FALSE,"RF20";"rf20a",#N/A,FALSE,"RF20A";"rf21",#N/A,FALSE,"RF21";"rf21a",#N/A,FALSE,"RF21A";"rf21b",#N/A,FALSE,"RF21B";"rf22",#N/A,FALSE,"RF22";"rf22a",#N/A,FALSE,"RF22A";"rf22b",#N/A,FALSE,"RF22B"}</definedName>
-    <definedName name="Kg_Almas">'[15]% alma'!$D$3:$F$51</definedName>
-    <definedName name="KgxTurL3_Fam">'[15]Kg por turno'!$A$70:$C$112</definedName>
-    <definedName name="KgxTurW_fam">'[15]Kg por turno'!$A$145:$C$159</definedName>
-    <definedName name="kk" hidden="1">'[16]suppl-pack'!#REF!</definedName>
+    <definedName name="Kg_Almas">'[14]% alma'!$D$3:$F$51</definedName>
+    <definedName name="KgxTurL3_Fam">'[14]Kg por turno'!$A$70:$C$112</definedName>
+    <definedName name="KgxTurW_fam">'[14]Kg por turno'!$A$145:$C$159</definedName>
+    <definedName name="kk" hidden="1">'[15]suppl-pack'!#REF!</definedName>
     <definedName name="kkkkkkkkk" hidden="1">{#N/A,#N/A,FALSE,"L&amp;M Performance";#N/A,#N/A,FALSE,"Brand Performance";#N/A,#N/A,FALSE,"Marlboro Performance"}</definedName>
     <definedName name="kl" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
-    <definedName name="KPI_2007_2">'[7]KPI 2007'!$B$4:$FJ$112</definedName>
+    <definedName name="KPI_2007_2">'[6]KPI 2007'!$B$4:$FJ$112</definedName>
     <definedName name="kraft" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="ks" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="KSKS" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
-    <definedName name="L_1">'[17]Horno 1'!$AR$8:$AT$22</definedName>
-    <definedName name="L_2">'[18]Horno 2'!$AR$8:$AR$23</definedName>
-    <definedName name="L_3">'[18]Horno 3'!$AR$8:$AR$23</definedName>
-    <definedName name="L_4">'[18]Horno 4'!$AR$8:$AR$17</definedName>
-    <definedName name="L_5">'[16]Horno 5'!$AY$8:$AY$35</definedName>
+    <definedName name="L_1">'[16]Horno 1'!$AR$8:$AT$22</definedName>
+    <definedName name="L_2">'[17]Horno 2'!$AR$8:$AR$23</definedName>
+    <definedName name="L_3">'[17]Horno 3'!$AR$8:$AR$23</definedName>
+    <definedName name="L_4">'[17]Horno 4'!$AR$8:$AR$17</definedName>
+    <definedName name="L_5">'[15]Horno 5'!$AY$8:$AY$35</definedName>
     <definedName name="Lease_Expense">#REF!</definedName>
     <definedName name="Lease_expenses">#REF!</definedName>
     <definedName name="lfsq" hidden="1">{"rf19",#N/A,FALSE,"RF19";"rf20",#N/A,FALSE,"RF20";"rf20a",#N/A,FALSE,"RF20A";"rf21",#N/A,FALSE,"RF21";"rf21a",#N/A,FALSE,"RF21A";"rf21b",#N/A,FALSE,"RF21B";"rf22",#N/A,FALSE,"RF22";"rf22a",#N/A,FALSE,"RF22A";"rf22b",#N/A,FALSE,"RF22B"}</definedName>
@@ -650,7 +650,7 @@
     <definedName name="nnnnnnnnnnn" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="Nori" hidden="1">{#N/A,#N/A,FALSE,"L&amp;M Performance";#N/A,#N/A,FALSE,"Brand Performance";#N/A,#N/A,FALSE,"Marlboro Performance"}</definedName>
     <definedName name="notcovered" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
-    <definedName name="nov">[7]NOV!$C$6:$DM$146</definedName>
+    <definedName name="nov">[6]NOV!$C$6:$DM$146</definedName>
     <definedName name="ñp" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="NUEVO" hidden="1">{"rf19",#N/A,FALSE,"RF19";"rf20",#N/A,FALSE,"RF20";"rf20a",#N/A,FALSE,"RF20A";"rf21",#N/A,FALSE,"RF21";"rf21a",#N/A,FALSE,"RF21A";"rf21b",#N/A,FALSE,"RF21B";"rf22",#N/A,FALSE,"RF22";"rf22a",#N/A,FALSE,"RF22A";"rf22b",#N/A,FALSE,"RF22B"}</definedName>
     <definedName name="o" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
@@ -684,7 +684,7 @@
     <definedName name="plo" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="PO" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="poi" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
-    <definedName name="POIJ" hidden="1">'[4]sov tot'!#REF!</definedName>
+    <definedName name="POIJ" hidden="1">'[3]sov tot'!#REF!</definedName>
     <definedName name="pol" hidden="1">{"rf19",#N/A,FALSE,"RF19";"rf20",#N/A,FALSE,"RF20";"rf20a",#N/A,FALSE,"RF20A";"rf21",#N/A,FALSE,"RF21";"rf21a",#N/A,FALSE,"RF21A";"rf21b",#N/A,FALSE,"RF21B";"rf22",#N/A,FALSE,"RF22";"rf22a",#N/A,FALSE,"RF22A";"rf22b",#N/A,FALSE,"RF22B"}</definedName>
     <definedName name="POO" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="pop" hidden="1">{"rf19",#N/A,FALSE,"RF19";"rf20",#N/A,FALSE,"RF20";"rf20a",#N/A,FALSE,"RF20A";"rf21",#N/A,FALSE,"RF21";"rf21a",#N/A,FALSE,"RF21A";"rf21b",#N/A,FALSE,"RF21B";"rf22",#N/A,FALSE,"RF22";"rf22a",#N/A,FALSE,"RF22A";"rf22b",#N/A,FALSE,"RF22B"}</definedName>
@@ -702,7 +702,7 @@
     <definedName name="Product" hidden="1">#REF!</definedName>
     <definedName name="Productivity" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="PROG_CHOCOLATERIA">#REF!</definedName>
-    <definedName name="PROG_GALLETERIA">[10]galleteria!#REF!</definedName>
+    <definedName name="PROG_GALLETERIA">[9]galleteria!#REF!</definedName>
     <definedName name="projout" hidden="1">{"rf19",#N/A,FALSE,"RF19";"rf20",#N/A,FALSE,"RF20";"rf20a",#N/A,FALSE,"RF20A";"rf21",#N/A,FALSE,"RF21";"rf21a",#N/A,FALSE,"RF21A";"rf21b",#N/A,FALSE,"RF21B";"rf22",#N/A,FALSE,"RF22";"rf22a",#N/A,FALSE,"RF22A";"rf22b",#N/A,FALSE,"RF22B"}</definedName>
     <definedName name="Proyvta">#REF!</definedName>
     <definedName name="Proyvta01">#REF!</definedName>
@@ -711,7 +711,7 @@
     <definedName name="Puta" hidden="1">{"rf19",#N/A,FALSE,"RF19";"rf20",#N/A,FALSE,"RF20";"rf20a",#N/A,FALSE,"RF20A";"rf21",#N/A,FALSE,"RF21";"rf21a",#N/A,FALSE,"RF21A";"rf21b",#N/A,FALSE,"RF21B";"rf22",#N/A,FALSE,"RF22";"rf22a",#N/A,FALSE,"RF22A";"rf22b",#N/A,FALSE,"RF22B"}</definedName>
     <definedName name="q" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="qa" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
-    <definedName name="qazee" hidden="1">'[4]sov tot'!#REF!</definedName>
+    <definedName name="qazee" hidden="1">'[3]sov tot'!#REF!</definedName>
     <definedName name="qe" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="QER" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="qfsdfc" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
@@ -721,13 +721,13 @@
     <definedName name="qqqqqqqqqq" hidden="1">{#N/A,#N/A,FALSE,"Summary"}</definedName>
     <definedName name="qqqqqqqqqqq" hidden="1">{#N/A,#N/A,FALSE,"L&amp;M Performance";#N/A,#N/A,FALSE,"Brand Performance";#N/A,#N/A,FALSE,"Marlboro Performance"}</definedName>
     <definedName name="qs" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
-    <definedName name="QSDRE" hidden="1">'[4]sov tot'!#REF!</definedName>
+    <definedName name="QSDRE" hidden="1">'[3]sov tot'!#REF!</definedName>
     <definedName name="qw" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
-    <definedName name="R_1">'[18]Horno 1'!$AR$8:$AT$22</definedName>
-    <definedName name="R_2">'[18]Horno 2'!$AR$8:$AT$23</definedName>
-    <definedName name="R_3">'[18]Horno 3'!$AR$8:$AT$23</definedName>
-    <definedName name="R_4">'[18]Horno 4'!$AR$8:$AU$16</definedName>
-    <definedName name="R_5">'[16]Horno 5'!$AY$8:$BB$35</definedName>
+    <definedName name="R_1">'[17]Horno 1'!$AR$8:$AT$22</definedName>
+    <definedName name="R_2">'[17]Horno 2'!$AR$8:$AT$23</definedName>
+    <definedName name="R_3">'[17]Horno 3'!$AR$8:$AT$23</definedName>
+    <definedName name="R_4">'[17]Horno 4'!$AR$8:$AU$16</definedName>
+    <definedName name="R_5">'[15]Horno 5'!$AY$8:$BB$35</definedName>
     <definedName name="ra" hidden="1">#REF!</definedName>
     <definedName name="RCArea" hidden="1">#REF!</definedName>
     <definedName name="Rec" hidden="1">{#N/A,#N/A,FALSE,"L&amp;M Performance";#N/A,#N/A,FALSE,"Brand Performance";#N/A,#N/A,FALSE,"Marlboro Performance"}</definedName>
@@ -815,13 +815,13 @@
     <definedName name="ti" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="Tit_Project">#REF!</definedName>
     <definedName name="Title">#REF!</definedName>
-    <definedName name="TonxTurB2">[15]Sheet1!$D$3:$I$44</definedName>
-    <definedName name="TonxTurB3">[15]Sheet1!$D$45:$I$69</definedName>
-    <definedName name="TonxTurL1">[15]Sheet1!$D$70:$I$101</definedName>
-    <definedName name="TonxTurL2">[15]Sheet1!$D$102:$I$165</definedName>
-    <definedName name="TonxTurL3">[15]Sheet1!$D$166:$I$240</definedName>
-    <definedName name="TonXTurL4">[15]Sheet1!$D$241:$I$305</definedName>
-    <definedName name="TonxTurW">[15]Sheet1!$D$306:$I$325</definedName>
+    <definedName name="TonxTurB2">[14]Sheet1!$D$3:$I$44</definedName>
+    <definedName name="TonxTurB3">[14]Sheet1!$D$45:$I$69</definedName>
+    <definedName name="TonxTurL1">[14]Sheet1!$D$70:$I$101</definedName>
+    <definedName name="TonxTurL2">[14]Sheet1!$D$102:$I$165</definedName>
+    <definedName name="TonxTurL3">[14]Sheet1!$D$166:$I$240</definedName>
+    <definedName name="TonXTurL4">[14]Sheet1!$D$241:$I$305</definedName>
+    <definedName name="TonxTurW">[14]Sheet1!$D$306:$I$325</definedName>
     <definedName name="toro" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="Total_Ano0">#REF!</definedName>
     <definedName name="Total_Cash">#REF!</definedName>
@@ -843,7 +843,7 @@
     <definedName name="trds7" hidden="1">#REF!</definedName>
     <definedName name="tttttttttttt" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="ttttttttttttttttttttttttt" hidden="1">{#N/A,#N/A,FALSE,"Summary"}</definedName>
-    <definedName name="uiu" hidden="1">'[16]suppl-pack'!#REF!</definedName>
+    <definedName name="uiu" hidden="1">'[15]suppl-pack'!#REF!</definedName>
     <definedName name="ujj" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="Uno" hidden="1">{"rf19",#N/A,FALSE,"RF19";"rf20",#N/A,FALSE,"RF20";"rf20a",#N/A,FALSE,"RF20A";"rf21",#N/A,FALSE,"RF21";"rf21a",#N/A,FALSE,"RF21A";"rf21b",#N/A,FALSE,"RF21B";"rf22",#N/A,FALSE,"RF22";"rf22a",#N/A,FALSE,"RF22A";"rf22b",#N/A,FALSE,"RF22B"}</definedName>
     <definedName name="uruguay" hidden="1">{"rf19",#N/A,FALSE,"RF19";"rf20",#N/A,FALSE,"RF20";"rf20a",#N/A,FALSE,"RF20A";"rf21",#N/A,FALSE,"RF21";"rf21a",#N/A,FALSE,"RF21A";"rf21b",#N/A,FALSE,"RF21B";"rf22",#N/A,FALSE,"RF22";"rf22a",#N/A,FALSE,"RF22A";"rf22b",#N/A,FALSE,"RF22B"}</definedName>
@@ -895,7 +895,7 @@
     <definedName name="W_Set_15C">#REF!</definedName>
     <definedName name="W_Set_16C">#REF!</definedName>
     <definedName name="wa" hidden="1">{"test","Core Scenario",FALSE,"Cash Flow Analysis"}</definedName>
-    <definedName name="Wafer">[18]Wafer!$AR$8:$AR$18</definedName>
+    <definedName name="Wafer">[17]Wafer!$AR$8:$AR$18</definedName>
     <definedName name="Waterfall" hidden="1">{"rf19",#N/A,FALSE,"RF19";"rf20",#N/A,FALSE,"RF20";"rf20a",#N/A,FALSE,"RF20A";"rf21",#N/A,FALSE,"RF21";"rf21a",#N/A,FALSE,"RF21A";"rf21b",#N/A,FALSE,"RF21B";"rf22",#N/A,FALSE,"RF22";"rf22a",#N/A,FALSE,"RF22A";"rf22b",#N/A,FALSE,"RF22B"}</definedName>
     <definedName name="we" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="weekly" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
@@ -956,7 +956,7 @@
     <definedName name="WWER" hidden="1">{"test","Core Scenario",FALSE,"Cash Flow Analysis"}</definedName>
     <definedName name="WWWW" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="wwwwwwwww" hidden="1">{#N/A,#N/A,FALSE,"L&amp;M Performance";#N/A,#N/A,FALSE,"Brand Performance";#N/A,#N/A,FALSE,"Marlboro Performance"}</definedName>
-    <definedName name="XCDER" hidden="1">'[4]sov tot'!#REF!</definedName>
+    <definedName name="XCDER" hidden="1">'[3]sov tot'!#REF!</definedName>
     <definedName name="xcvzxczxzdczx" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="xddd" hidden="1">{#N/A,#N/A,FALSE,"Summary"}</definedName>
     <definedName name="xx" hidden="1">#REF!</definedName>
@@ -974,7 +974,7 @@
     <definedName name="Yield_2">#REF!</definedName>
     <definedName name="yt" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="YTD_2008">#REF!</definedName>
-    <definedName name="YTGBH" hidden="1">'[4]sov tot'!#REF!</definedName>
+    <definedName name="YTGBH" hidden="1">'[3]sov tot'!#REF!</definedName>
     <definedName name="yyyyyyyyyyyyyy" hidden="1">{#N/A,#N/A,FALSE,"L&amp;M Performance";#N/A,#N/A,FALSE,"Brand Performance";#N/A,#N/A,FALSE,"Marlboro Performance"}</definedName>
     <definedName name="z" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="Z_2AFD2E8D_3D03_4813_8B05_F9D4BE800E07_.wvu.PrintArea" hidden="1">#REF!</definedName>
@@ -987,7 +987,7 @@
     <definedName name="zdfbfa" hidden="1">{#N/A,#N/A,FALSE,"1997 P&amp;L(pk) (Atlanta)";#N/A,#N/A,FALSE,"ONGOING P&amp;L(PK)(Atlanta)"}</definedName>
     <definedName name="zm" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="zñ" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
-    <definedName name="zsxaq" hidden="1">'[4]sov tot'!#REF!</definedName>
+    <definedName name="zsxaq" hidden="1">'[3]sov tot'!#REF!</definedName>
     <definedName name="zx" hidden="1">{"Summary",#N/A,TRUE,"Summary";"quest",#N/A,TRUE,"quest";"ss",#N/A,TRUE,"subm.sheet.";"RF1",#N/A,TRUE,"RF1";"RF1A",#N/A,TRUE,"RF1A";"RF2",#N/A,TRUE,"RF2";"RF2A",#N/A,TRUE,"RF2A";"RF3",#N/A,TRUE,"RF3";"RF3A",#N/A,TRUE,"RF3A";"RF4",#N/A,TRUE,"RF4";"RF4A",#N/A,TRUE,"RF4A";"RF5",#N/A,TRUE,"RF5";"RF6",#N/A,TRUE,"RF6";"RF6A",#N/A,TRUE,"RF6A";"RF7",#N/A,TRUE,"RF7";"RF7A",#N/A,TRUE,"RF7A";"RF8",#N/A,TRUE,"RF8";"RF8A",#N/A,TRUE,"RF8A";"RF9",#N/A,TRUE,"RF9";"RF9A",#N/A,TRUE,"RF9A";"RF10",#N/A,TRUE,"RF10";"RF11As",#N/A,TRUE,"RF11As";"RF11Bs",#N/A,TRUE,"RF11Bs";"RF12",#N/A,TRUE,"RF12";"RF13",#N/A,TRUE,"RF13";"RF14",#N/A,TRUE,"RF14";"RF15",#N/A,TRUE,"RF15"}</definedName>
     <definedName name="zz" hidden="1">{"rf19",#N/A,FALSE,"RF19";"rf20",#N/A,FALSE,"RF20";"rf20a",#N/A,FALSE,"RF20A";"rf21",#N/A,FALSE,"RF21";"rf21a",#N/A,FALSE,"RF21A";"rf21b",#N/A,FALSE,"RF21B";"rf22",#N/A,FALSE,"RF22";"rf22a",#N/A,FALSE,"RF22A";"rf22b",#N/A,FALSE,"RF22B"}</definedName>
     <definedName name="zzzz" hidden="1">{"test","Core Scenario",FALSE,"Cash Flow Analysis"}</definedName>
@@ -2078,36 +2078,80 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Resumen"/>
-      <sheetName val="LIMA (N recursos)"/>
-      <sheetName val="LIMA (Man)"/>
-      <sheetName val="LIMA (v2)"/>
-      <sheetName val="List Skus 8373"/>
-      <sheetName val="Inf L1"/>
-      <sheetName val="LIMA"/>
-      <sheetName val="8373 APO vs O9  (v2)"/>
-      <sheetName val="8373 APO vs O9 "/>
-      <sheetName val="APO FG 8373"/>
-      <sheetName val="Co-producto L6"/>
-      <sheetName val="Inf L1 (1)"/>
-      <sheetName val="Routings L6"/>
-      <sheetName val="Inf L4"/>
-      <sheetName val="Inf L5"/>
-      <sheetName val="Inf L2"/>
-      <sheetName val="Inf L6"/>
-      <sheetName val="Inf CB"/>
-      <sheetName val="Rates AC"/>
-      <sheetName val="Anexo L2-CB"/>
-      <sheetName val="Details for line"/>
-      <sheetName val="Proyectos"/>
-      <sheetName val="ECC - Data Maestra"/>
-      <sheetName val="ECC Lote mínimo"/>
-      <sheetName val="Sequenze flavors"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Sheet4"/>
+      <sheetName val="Sheet5"/>
+      <sheetName val="Graficos CI"/>
+      <sheetName val="Sheet8"/>
+      <sheetName val="BSC Lima"/>
+      <sheetName val="JAN"/>
+      <sheetName val="FEB"/>
+      <sheetName val="MAR"/>
+      <sheetName val="I"/>
+      <sheetName val="APR"/>
+      <sheetName val="MAY"/>
+      <sheetName val="JUN"/>
+      <sheetName val="II"/>
+      <sheetName val="JUL"/>
+      <sheetName val="AGO"/>
+      <sheetName val="SEP"/>
+      <sheetName val="III"/>
+      <sheetName val="OCT"/>
+      <sheetName val="NOV"/>
+      <sheetName val="DEC"/>
+      <sheetName val="IV"/>
+      <sheetName val="AÑO_2013"/>
+      <sheetName val="MX Perdida"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Analisis PW"/>
+      <sheetName val="AÑO 2008"/>
+      <sheetName val="Sheet6"/>
+      <sheetName val="AÑO_2012"/>
+      <sheetName val="Año_2011"/>
+      <sheetName val="Rework used 2013"/>
+      <sheetName val="Rework used"/>
+      <sheetName val="MATCH_05vs06"/>
+      <sheetName val="Sheet3"/>
+      <sheetName val="AÑO_2009"/>
+      <sheetName val="Bañados 2012"/>
+      <sheetName val="Año 2010"/>
+      <sheetName val="GRAFICOS INDICADORES"/>
+      <sheetName val="Goals 2008"/>
+      <sheetName val="KPI 2007"/>
+      <sheetName val="Resumen Rw"/>
+      <sheetName val="Indicadores Linea"/>
+      <sheetName val="Menu Principal"/>
+      <sheetName val="KPI´s"/>
+      <sheetName val="Absenteism"/>
+      <sheetName val="Overtime"/>
+      <sheetName val="Safety"/>
+      <sheetName val="Waterfall"/>
+      <sheetName val="Prod_Vtas_ Stocks"/>
+      <sheetName val="Database Waterfall"/>
+      <sheetName val="OBJ 2010"/>
+      <sheetName val="Rev Quarter"/>
+      <sheetName val="Reporte Yield Chocolatería"/>
+      <sheetName val="Reporte Yield Galletería"/>
+      <sheetName val="Reporte Yield Planta"/>
+      <sheetName val="Reporte PC"/>
+      <sheetName val="Reporte PW"/>
+      <sheetName val="SKUs"/>
+      <sheetName val="Balances Acu"/>
+      <sheetName val="New Graf"/>
+      <sheetName val="Bañados 2010"/>
+      <sheetName val="Analisis GEN"/>
+      <sheetName val="Analisis L3"/>
+      <sheetName val="Analisis L5"/>
+      <sheetName val="Analisis L4"/>
+      <sheetName val="Graficas de Yield"/>
+      <sheetName val="Acum Mes 2013"/>
+      <sheetName val="Productividad"/>
+      <sheetName val="New Acumulado"/>
+      <sheetName val="Sheet7"/>
+      <sheetName val="LIST"/>
+      <sheetName val="97RESULT"/>
+      <sheetName val="OB Interest"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -2128,32 +2172,61 @@
       <sheetData sheetId="15"/>
       <sheetData sheetId="16"/>
       <sheetData sheetId="17"/>
-      <sheetData sheetId="18">
-        <row r="27">
-          <cell r="G27">
-            <v>5107.52159085122</v>
-          </cell>
-          <cell r="H27">
-            <v>4188.1677044980006</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="H28">
-            <v>919.35388635321954</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="H30">
-            <v>5400</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
       <sheetData sheetId="22"/>
       <sheetData sheetId="23"/>
       <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+      <sheetData sheetId="37"/>
+      <sheetData sheetId="38"/>
+      <sheetData sheetId="39"/>
+      <sheetData sheetId="40"/>
+      <sheetData sheetId="41"/>
+      <sheetData sheetId="42"/>
+      <sheetData sheetId="43"/>
+      <sheetData sheetId="44"/>
+      <sheetData sheetId="45"/>
+      <sheetData sheetId="46"/>
+      <sheetData sheetId="47"/>
+      <sheetData sheetId="48"/>
+      <sheetData sheetId="49"/>
+      <sheetData sheetId="50"/>
+      <sheetData sheetId="51"/>
+      <sheetData sheetId="52"/>
+      <sheetData sheetId="53"/>
+      <sheetData sheetId="54"/>
+      <sheetData sheetId="55"/>
+      <sheetData sheetId="56"/>
+      <sheetData sheetId="57"/>
+      <sheetData sheetId="58"/>
+      <sheetData sheetId="59"/>
+      <sheetData sheetId="60"/>
+      <sheetData sheetId="61"/>
+      <sheetData sheetId="62"/>
+      <sheetData sheetId="63"/>
+      <sheetData sheetId="64"/>
+      <sheetData sheetId="65"/>
+      <sheetData sheetId="66"/>
+      <sheetData sheetId="67"/>
+      <sheetData sheetId="68"/>
+      <sheetData sheetId="69"/>
+      <sheetData sheetId="70" refreshError="1"/>
+      <sheetData sheetId="71" refreshError="1"/>
+      <sheetData sheetId="72" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2162,34 +2235,6 @@
 <file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Summary"/>
-      <sheetName val="Pivot"/>
-      <sheetName val="Pivot2"/>
-      <sheetName val="Complete Portfolio"/>
-      <sheetName val="Data"/>
-      <sheetName val="Pariticipants"/>
-      <sheetName val="galleteria"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="PL 4 QTR"/>
       <sheetName val="QTD VOL &amp; REV"/>
@@ -2274,12 +2319,9 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="DATOS"/>
       <sheetName val="ManodeObraRESUMEN"/>
@@ -2480,7 +2522,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3323,7 +3365,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3362,7 +3404,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3671,7 +3713,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3744,7 +3786,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4020,7 +4062,7 @@
       <sheetName val="Riepilogo linee-direz BUD"/>
       <sheetName val="Month"/>
       <sheetName val="数据List"/>
-      <sheetName val="_x005f_x005f_x005F_x0000_"/>
+      <sheetName val="_x005f_x005f_x005f_x0000_"/>
       <sheetName val="HOME"/>
       <sheetName val="DIOH"/>
       <sheetName val="Settings"/>
@@ -7437,12 +7479,9 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
       <sheetName val="Horno 2"/>
@@ -7469,83 +7508,38 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Sheet2"/>
-      <sheetName val="Sheet4"/>
-      <sheetName val="Sheet5"/>
-      <sheetName val="Graficos CI"/>
-      <sheetName val="Sheet8"/>
-      <sheetName val="BSC Lima"/>
-      <sheetName val="JAN"/>
-      <sheetName val="FEB"/>
-      <sheetName val="MAR"/>
-      <sheetName val="I"/>
-      <sheetName val="APR"/>
-      <sheetName val="MAY"/>
-      <sheetName val="JUN"/>
-      <sheetName val="II"/>
-      <sheetName val="JUL"/>
-      <sheetName val="AGO"/>
-      <sheetName val="SEP"/>
-      <sheetName val="III"/>
-      <sheetName val="OCT"/>
-      <sheetName val="NOV"/>
-      <sheetName val="DEC"/>
-      <sheetName val="IV"/>
-      <sheetName val="AÑO_2013"/>
-      <sheetName val="MX Perdida"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="Analisis PW"/>
-      <sheetName val="AÑO 2008"/>
-      <sheetName val="Sheet6"/>
-      <sheetName val="AÑO_2012"/>
-      <sheetName val="Año_2011"/>
-      <sheetName val="Rework used 2013"/>
-      <sheetName val="Rework used"/>
-      <sheetName val="MATCH_05vs06"/>
-      <sheetName val="Sheet3"/>
-      <sheetName val="AÑO_2009"/>
-      <sheetName val="Bañados 2012"/>
-      <sheetName val="Año 2010"/>
-      <sheetName val="GRAFICOS INDICADORES"/>
-      <sheetName val="Goals 2008"/>
-      <sheetName val="KPI 2007"/>
-      <sheetName val="Resumen Rw"/>
-      <sheetName val="Indicadores Linea"/>
-      <sheetName val="Menu Principal"/>
-      <sheetName val="KPI´s"/>
-      <sheetName val="Absenteism"/>
-      <sheetName val="Overtime"/>
-      <sheetName val="Safety"/>
-      <sheetName val="Waterfall"/>
-      <sheetName val="Prod_Vtas_ Stocks"/>
-      <sheetName val="Database Waterfall"/>
-      <sheetName val="OBJ 2010"/>
-      <sheetName val="Rev Quarter"/>
-      <sheetName val="Reporte Yield Chocolatería"/>
-      <sheetName val="Reporte Yield Galletería"/>
-      <sheetName val="Reporte Yield Planta"/>
-      <sheetName val="Reporte PC"/>
-      <sheetName val="Reporte PW"/>
-      <sheetName val="SKUs"/>
-      <sheetName val="Balances Acu"/>
-      <sheetName val="New Graf"/>
-      <sheetName val="Bañados 2010"/>
-      <sheetName val="Analisis GEN"/>
-      <sheetName val="Analisis L3"/>
-      <sheetName val="Analisis L5"/>
-      <sheetName val="Analisis L4"/>
-      <sheetName val="Graficas de Yield"/>
-      <sheetName val="Acum Mes 2013"/>
-      <sheetName val="Productividad"/>
-      <sheetName val="New Acumulado"/>
-      <sheetName val="Sheet7"/>
-      <sheetName val="LIST"/>
-      <sheetName val="97RESULT"/>
-      <sheetName val="OB Interest"/>
+      <sheetName val="Resumen"/>
+      <sheetName val="LIMA (N recursos)"/>
+      <sheetName val="LIMA (Man)"/>
+      <sheetName val="LIMA (v2)"/>
+      <sheetName val="List Skus 8373"/>
+      <sheetName val="Inf L1"/>
+      <sheetName val="LIMA"/>
+      <sheetName val="8373 APO vs O9  (v2)"/>
+      <sheetName val="8373 APO vs O9 "/>
+      <sheetName val="APO FG 8373"/>
+      <sheetName val="Co-producto L6"/>
+      <sheetName val="Inf L1 (1)"/>
+      <sheetName val="Routings L6"/>
+      <sheetName val="Inf L4"/>
+      <sheetName val="Inf L5"/>
+      <sheetName val="Inf L2"/>
+      <sheetName val="Inf L6"/>
+      <sheetName val="Inf CB"/>
+      <sheetName val="Rates AC"/>
+      <sheetName val="Anexo L2-CB"/>
+      <sheetName val="Details for line"/>
+      <sheetName val="Proyectos"/>
+      <sheetName val="ECC - Data Maestra"/>
+      <sheetName val="ECC Lote mínimo"/>
+      <sheetName val="Sequenze flavors"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -7566,67 +7560,38 @@
       <sheetData sheetId="15"/>
       <sheetData sheetId="16"/>
       <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
+      <sheetData sheetId="18">
+        <row r="27">
+          <cell r="G27">
+            <v>5107.52159085122</v>
+          </cell>
+          <cell r="H27">
+            <v>4188.1677044980006</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="H28">
+            <v>919.35388635321954</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="H30">
+            <v>5400</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
       <sheetData sheetId="22"/>
       <sheetData sheetId="23"/>
       <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
-      <sheetData sheetId="35"/>
-      <sheetData sheetId="36"/>
-      <sheetData sheetId="37"/>
-      <sheetData sheetId="38"/>
-      <sheetData sheetId="39"/>
-      <sheetData sheetId="40"/>
-      <sheetData sheetId="41"/>
-      <sheetData sheetId="42"/>
-      <sheetData sheetId="43"/>
-      <sheetData sheetId="44"/>
-      <sheetData sheetId="45"/>
-      <sheetData sheetId="46"/>
-      <sheetData sheetId="47"/>
-      <sheetData sheetId="48"/>
-      <sheetData sheetId="49"/>
-      <sheetData sheetId="50"/>
-      <sheetData sheetId="51"/>
-      <sheetData sheetId="52"/>
-      <sheetData sheetId="53"/>
-      <sheetData sheetId="54"/>
-      <sheetData sheetId="55"/>
-      <sheetData sheetId="56"/>
-      <sheetData sheetId="57"/>
-      <sheetData sheetId="58"/>
-      <sheetData sheetId="59"/>
-      <sheetData sheetId="60"/>
-      <sheetData sheetId="61"/>
-      <sheetData sheetId="62"/>
-      <sheetData sheetId="63"/>
-      <sheetData sheetId="64"/>
-      <sheetData sheetId="65"/>
-      <sheetData sheetId="66"/>
-      <sheetData sheetId="67"/>
-      <sheetData sheetId="68"/>
-      <sheetData sheetId="69"/>
-      <sheetData sheetId="70" refreshError="1"/>
-      <sheetData sheetId="71" refreshError="1"/>
-      <sheetData sheetId="72" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -7901,7 +7866,7 @@
       <sheetName val="Product_Views"/>
       <sheetName val="Riepilogo linee-direz BUD"/>
       <sheetName val="数据List"/>
-      <sheetName val="_x005f_x005f_x005F_x0000_"/>
+      <sheetName val="_x005f_x005f_x005f_x0000_"/>
       <sheetName val="Month"/>
       <sheetName val="Settings"/>
       <sheetName val="Línea 1"/>
@@ -8012,7 +7977,6 @@
       <sheetName val="US"/>
       <sheetName val="WO CONV"/>
       <sheetName val="_x0000_"/>
-      <sheetName val="_x005f_x005f_x005f_x0000_"/>
       <sheetName val="_x005f_x005f_x005f_x005f_x005f_x005f_x005f_x0000_"/>
       <sheetName val="_x005f_x005f_x005f_x005f_x005f_x005f_x005f_x005f_x005f_x005f_"/>
     </sheetNames>
@@ -8288,7 +8252,7 @@
       <sheetData sheetId="268"/>
       <sheetData sheetId="269" refreshError="1"/>
       <sheetData sheetId="270" refreshError="1"/>
-      <sheetData sheetId="271"/>
+      <sheetData sheetId="271" refreshError="1"/>
       <sheetData sheetId="272" refreshError="1"/>
       <sheetData sheetId="273" refreshError="1"/>
       <sheetData sheetId="274" refreshError="1"/>
@@ -8401,18 +8365,14 @@
       <sheetData sheetId="381"/>
       <sheetData sheetId="382" refreshError="1"/>
       <sheetData sheetId="383" refreshError="1"/>
-      <sheetData sheetId="384" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Formula"/>
       <sheetName val="Base PRISM"/>
@@ -8447,12 +8407,9 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Graphs"/>
       <sheetName val="Sheet1"/>
@@ -8477,12 +8434,9 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="xxxxxx"/>
       <sheetName val="Consultas"/>
@@ -8553,7 +8507,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -8586,7 +8540,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -8623,12 +8577,9 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val=" 2003. Eventos en  Produccion"/>
       <sheetName val="Plan Anual de Produccion 05"/>
@@ -8720,6 +8671,31 @@
       <sheetData sheetId="41"/>
       <sheetData sheetId="42"/>
       <sheetData sheetId="43" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Summary"/>
+      <sheetName val="Pivot"/>
+      <sheetName val="Pivot2"/>
+      <sheetName val="Complete Portfolio"/>
+      <sheetName val="Data"/>
+      <sheetName val="Pariticipants"/>
+      <sheetName val="galleteria"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -8905,25 +8881,25 @@
     <tabColor rgb="FFCCCC00"/>
   </sheetPr>
   <dimension ref="A1:N104"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="45.42578125" customWidth="1"/>
-    <col min="5" max="5" width="32.85546875" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="53" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" customWidth="1"/>
-    <col min="9" max="9" width="24.140625" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" customWidth="1"/>
-    <col min="13" max="13" width="10.140625" customWidth="1"/>
-    <col min="14" max="14" width="18.5703125" customWidth="1"/>
+    <col min="1" max="1" width="16.54296875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="27.453125" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="45.453125" customWidth="1"/>
+    <col min="5" max="5" width="32.81640625" customWidth="1"/>
+    <col min="6" max="6" width="15.1796875" style="53" customWidth="1"/>
+    <col min="7" max="7" width="16.453125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="14.81640625" customWidth="1"/>
+    <col min="9" max="9" width="24.1796875" customWidth="1"/>
+    <col min="10" max="10" width="10.453125" customWidth="1"/>
+    <col min="11" max="11" width="11.1796875" customWidth="1"/>
+    <col min="13" max="13" width="10.1796875" customWidth="1"/>
+    <col min="14" max="14" width="18.54296875" customWidth="1"/>
     <col min="19" max="19" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8933,7 +8909,7 @@
       <c r="E1" s="2"/>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
         <v>1</v>
@@ -8949,7 +8925,7 @@
       </c>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
       <c r="B3" s="6"/>
       <c r="C3" s="9">
@@ -8963,7 +8939,7 @@
       </c>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="11"/>
       <c r="B4" s="2"/>
       <c r="C4" s="12">
@@ -8977,7 +8953,7 @@
       </c>
       <c r="F4" s="3"/>
     </row>
-    <row r="5" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14"/>
       <c r="B5" s="15"/>
       <c r="C5" s="16">
@@ -8991,7 +8967,7 @@
       </c>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3"/>
@@ -8999,7 +8975,7 @@
       <c r="E6" s="2"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="18" t="s">
         <v>12</v>
       </c>
@@ -9019,7 +8995,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="24" t="s">
         <v>12</v>
       </c>
@@ -9035,7 +9011,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="24" t="s">
         <v>12</v>
       </c>
@@ -9051,7 +9027,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="24" t="s">
         <v>12</v>
       </c>
@@ -9067,7 +9043,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="24"/>
       <c r="B11" s="25"/>
       <c r="C11" s="26"/>
@@ -9081,7 +9057,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="24"/>
       <c r="B12" s="25"/>
       <c r="C12" s="29"/>
@@ -9095,7 +9071,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="32" t="s">
         <v>12</v>
       </c>
@@ -9113,7 +9089,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="37" t="s">
         <v>12</v>
       </c>
@@ -9133,7 +9109,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="32" t="s">
         <v>12</v>
       </c>
@@ -9155,7 +9131,7 @@
       <c r="J15" s="46"/>
       <c r="K15" s="47"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="48"/>
       <c r="B16" s="49"/>
       <c r="C16" s="49"/>
@@ -9165,7 +9141,7 @@
       <c r="I16" s="50"/>
       <c r="J16" s="50"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="48"/>
       <c r="B17" s="49"/>
       <c r="C17" s="49"/>
@@ -9173,7 +9149,7 @@
       <c r="E17" s="49"/>
       <c r="F17" s="49"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="51" t="s">
         <v>12</v>
       </c>
@@ -9184,14 +9160,14 @@
       <c r="D18" s="53"/>
       <c r="E18" s="53"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="53"/>
       <c r="B19" s="53"/>
       <c r="C19" s="53"/>
       <c r="D19" s="53"/>
       <c r="E19" s="53"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C20" s="54" t="s">
         <v>36</v>
       </c>
@@ -9201,7 +9177,7 @@
       <c r="E20" s="56"/>
       <c r="F20" s="57"/>
     </row>
-    <row r="22" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="58" t="s">
         <v>38</v>
       </c>
@@ -9230,7 +9206,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>45</v>
       </c>
@@ -9251,7 +9227,7 @@
         <v>5103.5331688774604</v>
       </c>
       <c r="G23" s="66">
-        <f>+'[1]Rates AC'!G27</f>
+        <f>+'[18]Rates AC'!G27</f>
         <v>5107.52159085122</v>
       </c>
       <c r="H23" s="67">
@@ -9263,14 +9239,14 @@
         <v>1.566317412016406E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="E24" s="4"/>
       <c r="F24" s="53">
         <f>+F23*3</f>
         <v>15310.599506632381</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C25" s="54" t="s">
         <v>48</v>
       </c>
@@ -9280,10 +9256,10 @@
       <c r="E25" s="68"/>
       <c r="F25" s="57"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="E26" s="4"/>
     </row>
-    <row r="27" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="58" t="s">
         <v>38</v>
       </c>
@@ -9315,7 +9291,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>45</v>
       </c>
@@ -9336,7 +9312,7 @@
         <v>4184.8971984795098</v>
       </c>
       <c r="G28" s="66">
-        <f>+'[1]Rates AC'!H27</f>
+        <f>+'[18]Rates AC'!H27</f>
         <v>4188.1677044980006</v>
       </c>
       <c r="H28" s="67">
@@ -9352,7 +9328,7 @@
         <v>4.5555555555555518</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>50</v>
       </c>
@@ -9372,7 +9348,7 @@
         <v>918.63597039794195</v>
       </c>
       <c r="G29" s="66">
-        <f>+'[1]Rates AC'!H28</f>
+        <f>+'[18]Rates AC'!H28</f>
         <v>919.35388635321954</v>
       </c>
       <c r="H29" s="67">
@@ -9387,23 +9363,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="E30" s="4"/>
       <c r="G30" s="75">
         <f>G28/G29</f>
         <v>4.5555555555555562</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="E31" s="4"/>
       <c r="G31" s="4">
         <v>4.5555555555555598</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="E32" s="4"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="51" t="s">
         <v>52</v>
       </c>
@@ -9414,17 +9390,17 @@
       <c r="D33" s="53"/>
       <c r="E33" s="4"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="53"/>
       <c r="B34" s="53"/>
       <c r="C34" s="53"/>
       <c r="D34" s="53"/>
       <c r="E34" s="4"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="E35" s="4"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C36" s="54" t="s">
         <v>36</v>
       </c>
@@ -9434,17 +9410,17 @@
       <c r="E36" s="68"/>
       <c r="F36" s="57"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C37" s="76"/>
       <c r="D37" t="s">
         <v>55</v>
       </c>
       <c r="E37" s="4"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="E38" s="4"/>
     </row>
-    <row r="39" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="58" t="s">
         <v>38</v>
       </c>
@@ -9473,7 +9449,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>45</v>
       </c>
@@ -9491,7 +9467,7 @@
         <v>6285.0713897913702</v>
       </c>
       <c r="G40" s="80">
-        <f>+'[1]Rates AC'!H30</f>
+        <f>+'[18]Rates AC'!H30</f>
         <v>5400</v>
       </c>
       <c r="H40" s="67">
@@ -9503,13 +9479,13 @@
         <v>1.4814814814814814E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="E41" s="4"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="E42" s="4"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="51" t="s">
         <v>52</v>
       </c>
@@ -9520,17 +9496,17 @@
       <c r="D44" s="53"/>
       <c r="E44" s="4"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="53"/>
       <c r="B45" s="53"/>
       <c r="C45" s="53"/>
       <c r="D45" s="53"/>
       <c r="E45" s="4"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="E46" s="4"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C47" s="54" t="s">
         <v>36</v>
       </c>
@@ -9540,16 +9516,16 @@
       <c r="E47" s="68"/>
       <c r="F47" s="57"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D48" t="s">
         <v>55</v>
       </c>
       <c r="E48" s="4"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="E49" s="4"/>
     </row>
-    <row r="50" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="58" t="s">
         <v>38</v>
       </c>
@@ -9578,7 +9554,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>45</v>
       </c>
@@ -9606,12 +9582,12 @@
         <v>6.2685120369763026E-4</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="82" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="51" t="s">
         <v>12</v>
       </c>
@@ -9619,7 +9595,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="58" t="s">
         <v>38</v>
       </c>
@@ -9642,7 +9618,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>45</v>
       </c>
@@ -9665,10 +9641,10 @@
         <v>1.566317412016406E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="E61" s="4"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C62" s="54" t="s">
         <v>48</v>
       </c>
@@ -9678,10 +9654,10 @@
       <c r="E62" s="68"/>
       <c r="F62" s="57"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="E63" s="4"/>
     </row>
-    <row r="64" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="58" t="s">
         <v>38</v>
       </c>
@@ -9707,7 +9683,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>45</v>
       </c>
@@ -9734,7 +9710,7 @@
         <v>1.9101431853858614E-3</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>50</v>
       </c>
@@ -9761,13 +9737,13 @@
         <v>8.7017634000911507E-3</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C67" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="18" t="s">
         <v>12</v>
       </c>
@@ -9784,7 +9760,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="24" t="s">
         <v>12</v>
       </c>
@@ -9797,7 +9773,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="24" t="s">
         <v>12</v>
       </c>
@@ -9810,7 +9786,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="24" t="s">
         <v>12</v>
       </c>
@@ -9823,7 +9799,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="32" t="s">
         <v>12</v>
       </c>
@@ -9838,14 +9814,14 @@
         <v>24</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="48"/>
       <c r="B74" s="49"/>
       <c r="C74" s="29"/>
       <c r="D74" s="30"/>
       <c r="E74" s="29"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="51" t="s">
         <v>52</v>
       </c>
@@ -9853,7 +9829,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="58" t="s">
         <v>38</v>
       </c>
@@ -9876,7 +9852,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
         <v>45</v>
       </c>
@@ -9898,10 +9874,10 @@
         <v>1.4814814814814814E-3</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="G79" s="105"/>
     </row>
-    <row r="80" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="83" t="s">
         <v>12</v>
       </c>
@@ -9919,13 +9895,13 @@
       </c>
       <c r="G80" s="105"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="G81" s="105"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
       <c r="G82" s="105"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A83" s="51" t="s">
         <v>52</v>
       </c>
@@ -9937,7 +9913,7 @@
       <c r="E83" s="4"/>
       <c r="G83" s="105"/>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A84" s="53"/>
       <c r="B84" s="53"/>
       <c r="C84" s="53"/>
@@ -9945,7 +9921,7 @@
       <c r="E84" s="4"/>
       <c r="G84" s="105"/>
     </row>
-    <row r="85" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="58" t="s">
         <v>38</v>
       </c>
@@ -9968,7 +9944,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
         <v>45</v>
       </c>
@@ -9990,8 +9966,8 @@
         <v>6.2685120369763026E-4</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="88" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="88" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="83" t="s">
         <v>12</v>
       </c>
@@ -10008,12 +9984,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A92" s="84" t="s">
         <v>64</v>
       </c>
@@ -10033,7 +10009,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A93" s="89" t="s">
         <v>67</v>
       </c>
@@ -10053,12 +10029,12 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A94" s="89" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A96" s="90" t="s">
         <v>12</v>
       </c>
@@ -10091,7 +10067,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A97" s="90" t="s">
         <v>12</v>
       </c>
@@ -10127,7 +10103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A98" s="90" t="s">
         <v>75</v>
       </c>
@@ -10157,17 +10133,17 @@
         <v>82</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A100" s="95" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A103" s="9" t="s">
         <v>85</v>
       </c>
@@ -10178,7 +10154,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="104" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="96" t="s">
         <v>85</v>
       </c>
